--- a/base_datas/crescimento_medio_populacao_uf.xlsx
+++ b/base_datas/crescimento_medio_populacao_uf.xlsx
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>75.13856653176558</v>
+        <v>76.2376991727233</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>3.994709603172543</v>
+        <v>3.9942239995645</v>
       </c>
     </row>
     <row r="4">
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>45.54365618579842</v>
+        <v>46.68691377710899</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>74.1753204870068</v>
+        <v>74.9537917208165</v>
       </c>
     </row>
     <row r="6">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>6.672612083103249</v>
+        <v>6.774702686181805</v>
       </c>
     </row>
     <row r="7">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>16.45232594517258</v>
+        <v>16.83616066740283</v>
       </c>
     </row>
     <row r="8">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>36.46831573274186</v>
+        <v>37.11254221717126</v>
       </c>
     </row>
     <row r="9">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>19.19189143839406</v>
+        <v>19.70937302742563</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>23.60361352818062</v>
+        <v>24.38577735997094</v>
       </c>
     </row>
     <row r="11">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>17.21106985066123</v>
+        <v>17.3208442232086</v>
       </c>
     </row>
     <row r="12">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>9.80352197706134</v>
+        <v>10.01785575687197</v>
       </c>
     </row>
     <row r="13">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>28.19476697833834</v>
+        <v>28.99295712325216</v>
       </c>
     </row>
     <row r="14">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>43.5307578988621</v>
+        <v>44.70202765714374</v>
       </c>
     </row>
     <row r="15">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>42.2390327366607</v>
+        <v>43.15616449697345</v>
       </c>
     </row>
     <row r="16">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>10.2406135225511</v>
+        <v>10.4548455814802</v>
       </c>
     </row>
     <row r="17">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>13.28659109945595</v>
+        <v>13.47191529887441</v>
       </c>
     </row>
     <row r="18">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>9.336876157256226</v>
+        <v>9.463683086502584</v>
       </c>
     </row>
     <row r="19">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>8.664258861403463</v>
+        <v>8.962406822803894</v>
       </c>
     </row>
     <row r="20">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>27.21884312559019</v>
+        <v>27.28711999005838</v>
       </c>
     </row>
     <row r="21">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>14.21337688145139</v>
+        <v>14.45997929504171</v>
       </c>
     </row>
     <row r="22">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>9.359921873025145</v>
+        <v>9.341238030744885</v>
       </c>
     </row>
     <row r="23">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>107.0977981631887</v>
+        <v>112.9925025773158</v>
       </c>
     </row>
     <row r="24">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>3.308169762301453</v>
+        <v>3.32340703017389</v>
       </c>
     </row>
     <row r="25">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>27.73473613527262</v>
+        <v>29.24249346372554</v>
       </c>
     </row>
     <row r="26">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>15.85617368667835</v>
+        <v>16.08774079906155</v>
       </c>
     </row>
     <row r="27">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>20.52294671772099</v>
+        <v>20.78619336570246</v>
       </c>
     </row>
     <row r="28">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>14.93858787478158</v>
+        <v>15.12887425273941</v>
       </c>
     </row>
   </sheetData>
